--- a/data/analysis_pixtral_12b_no_reid/visual_event_eval_pixtral_12b_no_reid.xlsx
+++ b/data/analysis_pixtral_12b_no_reid/visual_event_eval_pixtral_12b_no_reid.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="49">
   <si>
     <t>event</t>
   </si>
@@ -686,19 +686,19 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C6">
         <v>0.6</v>
       </c>
       <c r="D6">
-        <v>0.667</v>
+        <v>0.545</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1746,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1780,6 +1780,23 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2044,7 +2061,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2078,6 +2095,23 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
       </c>
     </row>
